--- a/ABC突破切線圖表_20260616/ABC突破切線精選_20260616.xlsx
+++ b/ABC突破切線圖表_20260616/ABC突破切線精選_20260616.xlsx
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -118,6 +118,21 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -484,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -542,32 +557,406 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3520.TWO</t>
+          <t>3311.TW</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>華盈</t>
+          <t>閎暉</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>17.05</v>
+        <v>41.3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>16.03</v>
+        <v>39.75</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>6.34%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1620</v>
+        <v>3897</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.2</v>
+        <v>8.4</v>
       </c>
       <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>6191.TW</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>精成科</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>103</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>97.58</v>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>5.55%</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>21025</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3413.TW</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>京鼎</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>322</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4434</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>9933.TW</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>41.93</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>7999</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2338.TW</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>光罩</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10031</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1563.TW</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>巧新</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>8.11%</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>1142</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>3149.TW</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>正達</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>4095</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>2369.TW</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>菱生</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>14220</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2441.TW</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>超豐</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>3.76%</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>9274</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>2454.TW</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>4470</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>4396.25</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>10400</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2405.TW</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>輔信</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>0.67%</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4275</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>3037.TW</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>960</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>934</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>2.78%</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>15473</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -576,6 +965,17 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
